--- a/回後買上漲圖表(基礎版)_20260611/回後買上漲基礎版_20260611.xlsx
+++ b/回後買上漲圖表(基礎版)_20260611/回後買上漲基礎版_20260611.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -551,31 +551,31 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6156.TWO</t>
+          <t>2348.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>松上</t>
+          <t>海悅</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>20.45</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>19.45</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>4374</v>
+        <v>5857</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1339</v>
+        <v>1792</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>3.3</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>18.95</v>
+        <v>70.37</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -586,31 +586,31 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>5410.TWO</t>
+          <t>2537.TW</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>國眾</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>44.15</v>
+        <v>11.1</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>40.85</v>
+        <v>10.35</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>6520</v>
+        <v>9520</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>2171</v>
+        <v>2960</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>39.41</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,31 +621,31 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>6259.TWO</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>29.75</v>
+        <v>55.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>28.55</v>
+        <v>52.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4595</v>
+        <v>4166</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1616</v>
+        <v>1375</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>25.98</v>
+        <v>54.36</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -656,31 +656,31 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>1785.TWO</t>
+          <t>2413.TW</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>光洋科</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>145.5</v>
+        <v>59.6</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>140</v>
+        <v>56.8</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>31409</v>
+        <v>21164</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>15325</v>
+        <v>7438</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>143.55</v>
+        <v>51.21</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>2913.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>農林</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>48.5</v>
+        <v>11.45</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>48.3</v>
+        <v>11.15</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6213</v>
+        <v>12401</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3230</v>
+        <v>5773</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>43.91</v>
+        <v>11.01</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -726,31 +726,31 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>8071.TWO</t>
+          <t>6186.TWO</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>新潤</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>24.95</v>
+        <v>42</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>23.7</v>
+        <v>41.2</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>9600</v>
+        <v>3498</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>4986</v>
+        <v>1640</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>21.15</v>
+        <v>39.9</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -761,31 +761,31 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6469.TWO</t>
+          <t>6180.TWO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>大樹</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>47.05</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>76</v>
+        <v>43.55</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2013</v>
+        <v>2457</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1093</v>
+        <v>1316</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>72.38</v>
+        <v>41.11</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -796,31 +796,31 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>3003.TW</t>
+          <t>8476.TW</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>67</v>
+        <v>19.05</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>66.59999999999999</v>
+        <v>19</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2624</v>
+        <v>2789</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1868</v>
+        <v>1675</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>61.85</v>
+        <v>16.09</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -831,31 +831,31 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6174.TWO</t>
+          <t>2530.TW</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>51.7</v>
+        <v>20.25</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>51.6</v>
+        <v>19.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8266</v>
+        <v>2282</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6057</v>
+        <v>1359</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>45.12</v>
+        <v>19.74</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -866,31 +866,31 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>6239.TW</t>
+          <t>5508.TWO</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>永信建</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>333</v>
+        <v>57.5</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>328.5</v>
+        <v>54</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>17412</v>
+        <v>2885</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>14310</v>
+        <v>1794</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>312.2</v>
+        <v>49.69</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2528.TW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>226</v>
+        <v>22.35</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>225.5</v>
+        <v>22.05</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>22509</v>
+        <v>1427</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>22326</v>
+        <v>1490</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>217.72</v>
+        <v>21.76</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -936,31 +936,31 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>1227.TW</t>
+          <t>7788.TW</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>28.85</v>
+        <v>258.5</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>28.8</v>
+        <v>251.5</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2722</v>
+        <v>3199</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>3219</v>
+        <v>4889</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>28.35</v>
+        <v>204.12</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -971,68 +971,33 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2637.TW</t>
+          <t>5213.TWO</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>亞昕</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>78.3</v>
+        <v>23.7</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>78.2</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7246</v>
+        <v>1311</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10939</v>
+        <v>2156</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>72.77</v>
+        <v>23.64</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>2108.TW</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>南帝</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>2498</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>5043</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>28.23</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1053,7 +1018,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
